--- a/docs/data/beidan_26086_dashboard.xlsx
+++ b/docs/data/beidan_26086_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26086期 比赛看板（皇冠历史相同亚盘） — 2026-08-18</t>
+          <t>⚽ 北京单场26086期 比赛看板（皇冠历史相同亚盘） — 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -1264,20 +1264,24 @@
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>55%</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>受半球/一球</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1316,20 +1320,24 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1368,20 +1376,24 @@
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>45%</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1420,20 +1432,24 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1472,20 +1488,24 @@
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>45%</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26086_dashboard.xlsx
+++ b/docs/data/beidan_26086_dashboard.xlsx
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1464,7 +1508,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>08-19 18:00</t>
+          <t>08-19 18:30</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">

--- a/docs/data/beidan_26086_dashboard.xlsx
+++ b/docs/data/beidan_26086_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26086期 比赛看板（皇冠历史相同亚盘） — 2026-08-19</t>
+          <t>⚽ 北京单场26086期 比赛看板（皇冠历史相同亚盘） — 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1304,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -1360,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1416,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1472,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1528,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1584,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1640,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1696,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1752,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -1808,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -1864,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1920,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1976,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2032,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2088,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2124,7 +2184,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2144,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2180,7 +2244,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2200,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2236,7 +2304,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2256,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2292,7 +2364,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2312,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2348,7 +2424,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2368,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2404,7 +2484,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2424,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2460,7 +2544,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>08-20 07:30</t>
+          <t>08-20 07:40</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2480,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2536,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2572,7 +2664,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>08-20 08:00</t>
+          <t>08-20 08:25</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2592,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -2648,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2704,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2740,7 +2844,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>08-20 08:30</t>
+          <t>08-20 08:40</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2760,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2816,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2852,7 +2964,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>08-20 09:30</t>
+          <t>08-20 09:40</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2872,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2908,7 +3024,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>08-20 09:30</t>
+          <t>08-20 09:40</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2928,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2964,7 +3084,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>08-20 09:30</t>
+          <t>08-20 09:40</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2984,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3020,7 +3144,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>08-20 10:30</t>
+          <t>08-20 10:40</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3040,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3076,7 +3204,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>08-20 10:30</t>
+          <t>08-20 10:40</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3096,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3132,7 +3264,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>08-20 10:30</t>
+          <t>08-20 10:40</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3152,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3548,20 +3684,24 @@
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>39%</t>
         </is>
       </c>
     </row>
